--- a/Planeacion de proyecto/Analisis Financiero (Preliminar).xlsx
+++ b/Planeacion de proyecto/Analisis Financiero (Preliminar).xlsx
@@ -1,44 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Compa\Documents\2026A\APM\Proyecto-APM---2026-1S\Gestión de Producción\Corrección de entrega\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manto\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87EE9D1F-51F7-40FA-8A06-12E265836CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6017E433-1AB8-4AFF-AA3B-DFDBF6101F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{34CA9882-19DA-4025-A6B3-A5B193287BD3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15150" activeTab="1" xr2:uid="{34CA9882-19DA-4025-A6B3-A5B193287BD3}"/>
   </bookViews>
   <sheets>
     <sheet name="Adquisiciones" sheetId="1" r:id="rId1"/>
     <sheet name="EX+B" sheetId="2" r:id="rId2"/>
     <sheet name="FdC" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
   <si>
     <t>https://www.alibaba.com/product-detail/Best-Price-Automatic-Robot-Arm-Palletizer_1601631617072.html?spm=a2700.galleryofferlist.normal_offer.d_title.193f13a0KutoFH&amp;priceId=74ddbed55cf64861a03c5df9930f23ac</t>
   </si>
@@ -61,9 +50,6 @@
     <t>Licencias Studio 5000</t>
   </si>
   <si>
-    <t>Licencias Plant Simulator</t>
-  </si>
-  <si>
     <t>Adquisiciones</t>
   </si>
   <si>
@@ -137,6 +123,24 @@
   </si>
   <si>
     <t>VPN</t>
+  </si>
+  <si>
+    <t>Licencias Plant Simulation</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Salario del Equipo</t>
+  </si>
+  <si>
+    <t>https://costbrief.com/industrial-robot-costs-pricing/</t>
+  </si>
+  <si>
+    <t>https://www.rockwellautomation.com/en-pl/support/workforce-development-training/training-calendar.html</t>
+  </si>
+  <si>
+    <t>https://www.paxiom.com/blogs/robotic-palletizing/</t>
   </si>
 </sst>
 </file>
@@ -144,12 +148,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -183,6 +187,14 @@
       <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -249,50 +261,51 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -301,9 +314,11 @@
     <xf numFmtId="1" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+  <cellStyles count="3">
+    <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
+    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -327,7 +342,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -439,10 +454,10 @@
             <c:numRef>
               <c:f>FdC!$B$2:$B$21</c:f>
               <c:numCache>
-                <c:formatCode>"$"\ #,##0.00;[Red]\-"$"\ #,##0.00</c:formatCode>
+                <c:formatCode>"$"#,##0.00_);[Red]\("$"#,##0.00\)</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>-278129087</c:v>
+                  <c:v>-324741087</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>-53400000</c:v>
@@ -538,67 +553,67 @@
             <c:numRef>
               <c:f>FdC!$C$2:$C$21</c:f>
               <c:numCache>
-                <c:formatCode>"$"\ #,##0;[Red]\-"$"\ #,##0</c:formatCode>
+                <c:formatCode>"$"#,##0_);[Red]\("$"#,##0\)</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>73000000</c:v>
+                  <c:v>87000000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>73000000</c:v>
+                  <c:v>87000000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>73000000</c:v>
+                  <c:v>87000000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>73000000</c:v>
+                  <c:v>87000000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>73000000</c:v>
+                  <c:v>87000000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>73000000</c:v>
+                  <c:v>87000000</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>73000000</c:v>
+                  <c:v>87000000</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>73000000</c:v>
+                  <c:v>87000000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>73000000</c:v>
+                  <c:v>87000000</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>73000000</c:v>
+                  <c:v>87000000</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>73000000</c:v>
+                  <c:v>87000000</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>73000000</c:v>
+                  <c:v>87000000</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>73000000</c:v>
+                  <c:v>87000000</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>73000000</c:v>
+                  <c:v>87000000</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>73000000</c:v>
+                  <c:v>87000000</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>73000000</c:v>
+                  <c:v>87000000</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>73000000</c:v>
+                  <c:v>87000000</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>73000000</c:v>
+                  <c:v>87000000</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>73000000</c:v>
+                  <c:v>87000000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -637,67 +652,67 @@
             <c:numRef>
               <c:f>FdC!$D$2:$D$21</c:f>
               <c:numCache>
-                <c:formatCode>"$"\ #,##0;[Red]\-"$"\ #,##0</c:formatCode>
+                <c:formatCode>"$"#,##0_);[Red]\("$"#,##0\)</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>-278129087</c:v>
+                  <c:v>-324741087</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>19600000</c:v>
+                  <c:v>33600000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>19600000</c:v>
+                  <c:v>33600000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19600000</c:v>
+                  <c:v>33600000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>19600000</c:v>
+                  <c:v>33600000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>19600000</c:v>
+                  <c:v>33600000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>19600000</c:v>
+                  <c:v>33600000</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>19600000</c:v>
+                  <c:v>33600000</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>19600000</c:v>
+                  <c:v>33600000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>19600000</c:v>
+                  <c:v>33600000</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>19600000</c:v>
+                  <c:v>33600000</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>19600000</c:v>
+                  <c:v>33600000</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>19600000</c:v>
+                  <c:v>33600000</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>19600000</c:v>
+                  <c:v>33600000</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>19600000</c:v>
+                  <c:v>33600000</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>19600000</c:v>
+                  <c:v>33600000</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>19600000</c:v>
+                  <c:v>33600000</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>19600000</c:v>
+                  <c:v>33600000</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>19600000</c:v>
+                  <c:v>33600000</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>19600000</c:v>
+                  <c:v>33600000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -736,67 +751,67 @@
             <c:numRef>
               <c:f>FdC!$E$2:$E$21</c:f>
               <c:numCache>
-                <c:formatCode>"$"\ #,##0;[Red]\-"$"\ #,##0</c:formatCode>
+                <c:formatCode>"$"#,##0_);[Red]\("$"#,##0\)</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>-278129087</c:v>
+                  <c:v>-324741087</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-258529087</c:v>
+                  <c:v>-291141087</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-238929087</c:v>
+                  <c:v>-257541087</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-219329087</c:v>
+                  <c:v>-223941087</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-199729087</c:v>
+                  <c:v>-190341087</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-180129087</c:v>
+                  <c:v>-156741087</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-160529087</c:v>
+                  <c:v>-123141087</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-140929087</c:v>
+                  <c:v>-89541087</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-121329087</c:v>
+                  <c:v>-55941087</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-101729087</c:v>
+                  <c:v>-22341087</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-82129087</c:v>
+                  <c:v>11258913</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-62529087</c:v>
+                  <c:v>44858913</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-42929087</c:v>
+                  <c:v>78458913</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-23329087</c:v>
+                  <c:v>112058913</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-3729087</c:v>
+                  <c:v>145658913</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>15870913</c:v>
+                  <c:v>179258913</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>35470913</c:v>
+                  <c:v>212858913</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>55070913</c:v>
+                  <c:v>246458913</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>74670913</c:v>
+                  <c:v>280058913</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>94270913</c:v>
+                  <c:v>313658913</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1712,9 +1727,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1752,7 +1767,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1858,7 +1873,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2000,7 +2015,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2009,29 +2024,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC626771-BBF1-4BDA-AE97-3F55ED6FC1BC}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.6640625" style="1" customWidth="1"/>
-    <col min="2" max="3" width="18.5546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="231.88671875" style="3" customWidth="1"/>
-    <col min="5" max="16384" width="11.44140625" style="1"/>
+    <col min="1" max="1" width="52.7109375" style="1" customWidth="1"/>
+    <col min="2" max="3" width="18.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="231.85546875" style="3" customWidth="1"/>
+    <col min="5" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="8" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="8" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2047,15 +2062,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2063,35 +2078,35 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55B1E273-002F-44CB-B87B-B9FBB131734B}">
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.109375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="26.140625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" style="5" customWidth="1"/>
     <col min="3" max="3" width="12" style="4" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="14.88671875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="11.44140625" style="4"/>
-    <col min="7" max="7" width="45.109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="30.28515625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" style="4"/>
+    <col min="7" max="7" width="45.140625" style="4" customWidth="1"/>
     <col min="8" max="8" width="15" style="4" customWidth="1"/>
-    <col min="9" max="16384" width="11.44140625" style="4"/>
+    <col min="9" max="16384" width="11.42578125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" s="20"/>
       <c r="D1" s="20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E1" s="20"/>
       <c r="G1" s="20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H1" s="20"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -2110,53 +2125,71 @@
       <c r="H2" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J2" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="5">
         <v>5000000</v>
       </c>
+      <c r="C3" s="23" t="s">
+        <v>35</v>
+      </c>
       <c r="D3" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" s="4">
         <f>Adquisiciones!C2</f>
         <v>262129087.00000003</v>
       </c>
       <c r="G3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="4">
+        <f>3000000*12*2</f>
+        <v>72000000</v>
+      </c>
+      <c r="I3" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="H3" s="4">
-        <f>2000000*12*2</f>
-        <v>48000000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>10</v>
       </c>
       <c r="B4" s="5">
         <f>(9)*16*750*300</f>
         <v>32400000</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E4" s="4">
-        <f>3000000*2</f>
-        <v>6000000</v>
+        <f>(2236+3904+2236+2236)*1000</f>
+        <v>10612000</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>36</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H4" s="4">
         <f>5000000</f>
         <v>5000000</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J4" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -2165,46 +2198,65 @@
         <v>10000000</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E5" s="4">
-        <f>10000000*1</f>
-        <v>10000000</v>
+        <f>(10000)*4000</f>
+        <v>40000000</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H5" s="4">
         <v>5000000</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J5" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="B6" s="5">
         <f>1500*4000</f>
         <v>6000000</v>
       </c>
+      <c r="D6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="4">
+        <f>6*2000000</f>
+        <v>12000000</v>
+      </c>
       <c r="G6" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H6" s="4">
-        <v>15000000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>5000000</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <f>SUM(B3:B6)</f>
         <v>53400000</v>
       </c>
       <c r="E7" s="4">
         <f>SUM(E3:E6)</f>
-        <v>278129087</v>
+        <v>324741087</v>
       </c>
       <c r="H7" s="4">
         <f xml:space="preserve"> SUM(H3:H6)</f>
-        <v>73000000</v>
+        <v>87000000</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2213,6 +2265,12 @@
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="G1:H1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="F5" r:id="rId1" xr:uid="{ADF784E2-68FC-4B2E-BCC1-790BF86EB68D}"/>
+    <hyperlink ref="F4" r:id="rId2" xr:uid="{56839E54-40A4-4628-8AAC-3904428C1DDE}"/>
+    <hyperlink ref="I3" r:id="rId3" xr:uid="{B11B17C2-FF5D-44CB-B7DB-FF30F443A4AC}"/>
+    <hyperlink ref="C3" r:id="rId4" xr:uid="{EAE665CA-5E6D-4F56-A17C-97822EF828F6}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2220,54 +2278,54 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE4FD7C4-7C36-405F-988D-68A540A30D5D}">
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" style="6" customWidth="1"/>
-    <col min="2" max="2" width="17.88671875" style="7" customWidth="1"/>
-    <col min="3" max="3" width="17.6640625" style="15" customWidth="1"/>
-    <col min="4" max="4" width="17.44140625" style="15" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" style="15" customWidth="1"/>
-    <col min="6" max="16384" width="11.44140625" style="4"/>
+    <col min="2" max="2" width="17.85546875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="15" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" style="15" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" style="15" customWidth="1"/>
+    <col min="6" max="16384" width="11.42578125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C1" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="14" t="s">
-        <v>21</v>
-      </c>
       <c r="E1" s="14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="13">
         <v>1</v>
       </c>
       <c r="B2" s="7">
         <f>'EX+B'!E7*-1</f>
-        <v>-278129087</v>
+        <v>-324741087</v>
       </c>
       <c r="C2" s="15">
         <v>0</v>
       </c>
       <c r="D2" s="15">
         <f t="shared" ref="D2:D21" si="0">SUM(B2:C2)</f>
-        <v>-278129087</v>
+        <v>-324741087</v>
       </c>
       <c r="E2" s="15">
         <f>D2</f>
-        <v>-278129087</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>-324741087</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="13">
         <v>2</v>
       </c>
@@ -2277,18 +2335,18 @@
       </c>
       <c r="C3" s="15">
         <f>'EX+B'!H7</f>
-        <v>73000000</v>
+        <v>87000000</v>
       </c>
       <c r="D3" s="15">
         <f t="shared" si="0"/>
-        <v>19600000</v>
+        <v>33600000</v>
       </c>
       <c r="E3" s="15">
         <f>E2+D3</f>
-        <v>-258529087</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>-291141087</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="13">
         <v>3</v>
       </c>
@@ -2298,18 +2356,18 @@
       </c>
       <c r="C4" s="15">
         <f>C3</f>
-        <v>73000000</v>
+        <v>87000000</v>
       </c>
       <c r="D4" s="15">
         <f t="shared" si="0"/>
-        <v>19600000</v>
+        <v>33600000</v>
       </c>
       <c r="E4" s="15">
         <f t="shared" ref="E4:E21" si="1">E3+D4</f>
-        <v>-238929087</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>-257541087</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
         <v>4</v>
       </c>
@@ -2319,18 +2377,18 @@
       </c>
       <c r="C5" s="15">
         <f t="shared" ref="C5:C21" si="3">C4</f>
-        <v>73000000</v>
+        <v>87000000</v>
       </c>
       <c r="D5" s="15">
         <f t="shared" si="0"/>
-        <v>19600000</v>
+        <v>33600000</v>
       </c>
       <c r="E5" s="15">
         <f t="shared" si="1"/>
-        <v>-219329087</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>-223941087</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="13">
         <v>5</v>
       </c>
@@ -2340,18 +2398,18 @@
       </c>
       <c r="C6" s="15">
         <f t="shared" si="3"/>
-        <v>73000000</v>
+        <v>87000000</v>
       </c>
       <c r="D6" s="15">
         <f t="shared" si="0"/>
-        <v>19600000</v>
+        <v>33600000</v>
       </c>
       <c r="E6" s="15">
         <f t="shared" si="1"/>
-        <v>-199729087</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>-190341087</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="13">
         <v>6</v>
       </c>
@@ -2361,18 +2419,18 @@
       </c>
       <c r="C7" s="15">
         <f t="shared" si="3"/>
-        <v>73000000</v>
+        <v>87000000</v>
       </c>
       <c r="D7" s="15">
         <f t="shared" si="0"/>
-        <v>19600000</v>
+        <v>33600000</v>
       </c>
       <c r="E7" s="15">
         <f t="shared" si="1"/>
-        <v>-180129087</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>-156741087</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="13">
         <v>7</v>
       </c>
@@ -2382,18 +2440,18 @@
       </c>
       <c r="C8" s="15">
         <f t="shared" si="3"/>
-        <v>73000000</v>
+        <v>87000000</v>
       </c>
       <c r="D8" s="15">
         <f t="shared" si="0"/>
-        <v>19600000</v>
+        <v>33600000</v>
       </c>
       <c r="E8" s="15">
         <f t="shared" si="1"/>
-        <v>-160529087</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>-123141087</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="13">
         <v>8</v>
       </c>
@@ -2403,18 +2461,18 @@
       </c>
       <c r="C9" s="15">
         <f t="shared" si="3"/>
-        <v>73000000</v>
+        <v>87000000</v>
       </c>
       <c r="D9" s="15">
         <f t="shared" si="0"/>
-        <v>19600000</v>
+        <v>33600000</v>
       </c>
       <c r="E9" s="15">
         <f t="shared" si="1"/>
-        <v>-140929087</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+        <v>-89541087</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="13">
         <v>9</v>
       </c>
@@ -2424,18 +2482,18 @@
       </c>
       <c r="C10" s="15">
         <f t="shared" si="3"/>
-        <v>73000000</v>
+        <v>87000000</v>
       </c>
       <c r="D10" s="15">
         <f t="shared" si="0"/>
-        <v>19600000</v>
+        <v>33600000</v>
       </c>
       <c r="E10" s="15">
         <f t="shared" si="1"/>
-        <v>-121329087</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+        <v>-55941087</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="13">
         <v>10</v>
       </c>
@@ -2445,18 +2503,18 @@
       </c>
       <c r="C11" s="15">
         <f t="shared" si="3"/>
-        <v>73000000</v>
+        <v>87000000</v>
       </c>
       <c r="D11" s="15">
         <f t="shared" si="0"/>
-        <v>19600000</v>
+        <v>33600000</v>
       </c>
       <c r="E11" s="15">
         <f t="shared" si="1"/>
-        <v>-101729087</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+        <v>-22341087</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="13">
         <v>11</v>
       </c>
@@ -2466,18 +2524,18 @@
       </c>
       <c r="C12" s="15">
         <f t="shared" si="3"/>
-        <v>73000000</v>
+        <v>87000000</v>
       </c>
       <c r="D12" s="15">
         <f t="shared" si="0"/>
-        <v>19600000</v>
+        <v>33600000</v>
       </c>
       <c r="E12" s="15">
         <f t="shared" si="1"/>
-        <v>-82129087</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+        <v>11258913</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="13">
         <v>12</v>
       </c>
@@ -2487,18 +2545,18 @@
       </c>
       <c r="C13" s="15">
         <f t="shared" si="3"/>
-        <v>73000000</v>
+        <v>87000000</v>
       </c>
       <c r="D13" s="15">
         <f t="shared" si="0"/>
-        <v>19600000</v>
+        <v>33600000</v>
       </c>
       <c r="E13" s="15">
         <f t="shared" si="1"/>
-        <v>-62529087</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+        <v>44858913</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="13">
         <v>13</v>
       </c>
@@ -2508,18 +2566,18 @@
       </c>
       <c r="C14" s="15">
         <f t="shared" si="3"/>
-        <v>73000000</v>
+        <v>87000000</v>
       </c>
       <c r="D14" s="15">
         <f t="shared" si="0"/>
-        <v>19600000</v>
+        <v>33600000</v>
       </c>
       <c r="E14" s="15">
         <f t="shared" si="1"/>
-        <v>-42929087</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+        <v>78458913</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
         <v>14</v>
       </c>
@@ -2529,18 +2587,18 @@
       </c>
       <c r="C15" s="15">
         <f t="shared" si="3"/>
-        <v>73000000</v>
+        <v>87000000</v>
       </c>
       <c r="D15" s="15">
         <f t="shared" si="0"/>
-        <v>19600000</v>
+        <v>33600000</v>
       </c>
       <c r="E15" s="15">
         <f t="shared" si="1"/>
-        <v>-23329087</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+        <v>112058913</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="13">
         <v>15</v>
       </c>
@@ -2550,18 +2608,18 @@
       </c>
       <c r="C16" s="15">
         <f t="shared" si="3"/>
-        <v>73000000</v>
+        <v>87000000</v>
       </c>
       <c r="D16" s="15">
         <f t="shared" si="0"/>
-        <v>19600000</v>
+        <v>33600000</v>
       </c>
       <c r="E16" s="15">
         <f t="shared" si="1"/>
-        <v>-3729087</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+        <v>145658913</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="13">
         <v>16</v>
       </c>
@@ -2571,18 +2629,18 @@
       </c>
       <c r="C17" s="15">
         <f t="shared" si="3"/>
-        <v>73000000</v>
+        <v>87000000</v>
       </c>
       <c r="D17" s="15">
         <f t="shared" si="0"/>
-        <v>19600000</v>
+        <v>33600000</v>
       </c>
       <c r="E17" s="15">
         <f t="shared" si="1"/>
-        <v>15870913</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+        <v>179258913</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="13">
         <v>17</v>
       </c>
@@ -2592,18 +2650,18 @@
       </c>
       <c r="C18" s="15">
         <f t="shared" si="3"/>
-        <v>73000000</v>
+        <v>87000000</v>
       </c>
       <c r="D18" s="15">
         <f t="shared" si="0"/>
-        <v>19600000</v>
+        <v>33600000</v>
       </c>
       <c r="E18" s="15">
         <f t="shared" si="1"/>
-        <v>35470913</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+        <v>212858913</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="13">
         <v>18</v>
       </c>
@@ -2613,18 +2671,18 @@
       </c>
       <c r="C19" s="15">
         <f t="shared" si="3"/>
-        <v>73000000</v>
+        <v>87000000</v>
       </c>
       <c r="D19" s="15">
         <f t="shared" si="0"/>
-        <v>19600000</v>
+        <v>33600000</v>
       </c>
       <c r="E19" s="15">
         <f t="shared" si="1"/>
-        <v>55070913</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+        <v>246458913</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="13">
         <v>19</v>
       </c>
@@ -2634,18 +2692,18 @@
       </c>
       <c r="C20" s="15">
         <f t="shared" si="3"/>
-        <v>73000000</v>
+        <v>87000000</v>
       </c>
       <c r="D20" s="15">
         <f t="shared" si="0"/>
-        <v>19600000</v>
+        <v>33600000</v>
       </c>
       <c r="E20" s="15">
         <f t="shared" si="1"/>
-        <v>74670913</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+        <v>280058913</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="13">
         <v>19</v>
       </c>
@@ -2655,65 +2713,65 @@
       </c>
       <c r="C21" s="15">
         <f t="shared" si="3"/>
-        <v>73000000</v>
+        <v>87000000</v>
       </c>
       <c r="D21" s="15">
         <f t="shared" si="0"/>
-        <v>19600000</v>
+        <v>33600000</v>
       </c>
       <c r="E21" s="15">
         <f t="shared" si="1"/>
-        <v>94270913</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+        <v>313658913</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="22"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
         <v>27</v>
-      </c>
-      <c r="B24" s="22"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="13" t="s">
-        <v>28</v>
       </c>
       <c r="B25" s="16">
         <v>0.10249999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" s="16">
         <f>-E17/D2</f>
-        <v>5.7063118321026236E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.55200564442281363</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" s="16">
         <f>IRR(D2:D17)</f>
-        <v>7.0183778708419187E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+        <v>6.074869593392096E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="17">
+        <f>A12+(-E12/D12)</f>
+        <v>10.664913303571428</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
         <v>31</v>
-      </c>
-      <c r="B28" s="17">
-        <f>A16+(-E16/D16)</f>
-        <v>15.190259540816326</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="13" t="s">
-        <v>32</v>
       </c>
       <c r="B29" s="18">
         <f>NPV(B25,D3:D21)+D2</f>
-        <v>-116855576.25684595</v>
+        <v>-48272211.440307319</v>
       </c>
     </row>
   </sheetData>

--- a/Planeacion de proyecto/Analisis Financiero (Preliminar).xlsx
+++ b/Planeacion de proyecto/Analisis Financiero (Preliminar).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manto\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6017E433-1AB8-4AFF-AA3B-DFDBF6101F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F7D1D3-71C3-4671-8B2C-CE82F1C2EC3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15150" activeTab="1" xr2:uid="{34CA9882-19DA-4025-A6B3-A5B193287BD3}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="20730" windowHeight="11310" activeTab="1" xr2:uid="{34CA9882-19DA-4025-A6B3-A5B193287BD3}"/>
   </bookViews>
   <sheets>
     <sheet name="Adquisiciones" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="56">
   <si>
     <t>https://www.alibaba.com/product-detail/Best-Price-Automatic-Robot-Arm-Palletizer_1601631617072.html?spm=a2700.galleryofferlist.normal_offer.d_title.193f13a0KutoFH&amp;priceId=74ddbed55cf64861a03c5df9930f23ac</t>
   </si>
@@ -140,7 +140,61 @@
     <t>https://www.rockwellautomation.com/en-pl/support/workforce-development-training/training-calendar.html</t>
   </si>
   <si>
-    <t>https://www.paxiom.com/blogs/robotic-palletizing/</t>
+    <t>https://www.paxiom.com/blogs/robotic-palletizing/ https://co.computrabajo.com/salarios/empacador</t>
+  </si>
+  <si>
+    <t>Licencias SiemensNX</t>
+  </si>
+  <si>
+    <t>https://openit.com/es/siemens-nx-reinvents-to-cater-to-aec-industrys-needs/</t>
+  </si>
+  <si>
+    <t>https://industrialmonitordirect.com/es/blogs/knowledgebase/studio-5000-license-cost-pricing-tiers-for-controllogix</t>
+  </si>
+  <si>
+    <t>SALARIO</t>
+  </si>
+  <si>
+    <t>Salario Base</t>
+  </si>
+  <si>
+    <t>ARL</t>
+  </si>
+  <si>
+    <t>Pensión</t>
+  </si>
+  <si>
+    <t>Salud</t>
+  </si>
+  <si>
+    <t>Caja de compensación</t>
+  </si>
+  <si>
+    <t>https://corporativo.compensar.com/afiliaciones/calculadora-aportes</t>
+  </si>
+  <si>
+    <t>Documentación</t>
+  </si>
+  <si>
+    <t>https://www.mxwholesale.co.uk/products/pallet-deal-504-x-coca-cola-original-bottles-1-5l-eu-6pk</t>
+  </si>
+  <si>
+    <t>PERDIDAS</t>
+  </si>
+  <si>
+    <t>Precio por Palet</t>
+  </si>
+  <si>
+    <t>Incidentes de Caida de Pallet Anual</t>
+  </si>
+  <si>
+    <t>https://pascosystems.com/resources/cost-savings-of-palletizing/</t>
+  </si>
+  <si>
+    <t>Aumentos por productividad</t>
+  </si>
+  <si>
+    <t>https://investors.coca-colafemsa.com/assets/files/reportes_resultados_esp/2020/190321-kof-estados-financieros-2020-final.pdf</t>
   </si>
 </sst>
 </file>
@@ -153,7 +207,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,8 +250,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -207,6 +266,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9A0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -266,7 +331,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -301,20 +366,29 @@
     <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -457,64 +531,64 @@
                 <c:formatCode>"$"#,##0.00_);[Red]\("$"#,##0.00\)</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>-324741087</c:v>
+                  <c:v>-281994387</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-53400000</c:v>
+                  <c:v>-52515288.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-53400000</c:v>
+                  <c:v>-52515288.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-53400000</c:v>
+                  <c:v>-52515288.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-53400000</c:v>
+                  <c:v>-52515288.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-53400000</c:v>
+                  <c:v>-52515288.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-53400000</c:v>
+                  <c:v>-52515288.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-53400000</c:v>
+                  <c:v>-52515288.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-53400000</c:v>
+                  <c:v>-52515288.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-53400000</c:v>
+                  <c:v>-52515288.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-53400000</c:v>
+                  <c:v>-52515288.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-53400000</c:v>
+                  <c:v>-52515288.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-53400000</c:v>
+                  <c:v>-52515288.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-53400000</c:v>
+                  <c:v>-52515288.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-53400000</c:v>
+                  <c:v>-52515288.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-53400000</c:v>
+                  <c:v>-52515288.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-53400000</c:v>
+                  <c:v>-52515288.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-53400000</c:v>
+                  <c:v>-52515288.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-53400000</c:v>
+                  <c:v>-52515288.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-53400000</c:v>
+                  <c:v>-52515288.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -559,61 +633,61 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>87000000</c:v>
+                  <c:v>88957030.508875743</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>87000000</c:v>
+                  <c:v>88957030.508875743</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>87000000</c:v>
+                  <c:v>88957030.508875743</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>87000000</c:v>
+                  <c:v>88957030.508875743</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>87000000</c:v>
+                  <c:v>88957030.508875743</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>87000000</c:v>
+                  <c:v>88957030.508875743</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>87000000</c:v>
+                  <c:v>88957030.508875743</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>87000000</c:v>
+                  <c:v>88957030.508875743</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>87000000</c:v>
+                  <c:v>88957030.508875743</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>87000000</c:v>
+                  <c:v>88957030.508875743</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>87000000</c:v>
+                  <c:v>88957030.508875743</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>87000000</c:v>
+                  <c:v>88957030.508875743</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>87000000</c:v>
+                  <c:v>88957030.508875743</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>87000000</c:v>
+                  <c:v>88957030.508875743</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>87000000</c:v>
+                  <c:v>88957030.508875743</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>87000000</c:v>
+                  <c:v>88957030.508875743</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>87000000</c:v>
+                  <c:v>88957030.508875743</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>87000000</c:v>
+                  <c:v>88957030.508875743</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>87000000</c:v>
+                  <c:v>88957030.508875743</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -655,64 +729,64 @@
                 <c:formatCode>"$"#,##0_);[Red]\("$"#,##0\)</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>-324741087</c:v>
+                  <c:v>-281994387</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>33600000</c:v>
+                  <c:v>36441742.008875743</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>33600000</c:v>
+                  <c:v>36441742.008875743</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>33600000</c:v>
+                  <c:v>36441742.008875743</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>33600000</c:v>
+                  <c:v>36441742.008875743</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>33600000</c:v>
+                  <c:v>36441742.008875743</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>33600000</c:v>
+                  <c:v>36441742.008875743</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>33600000</c:v>
+                  <c:v>36441742.008875743</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>33600000</c:v>
+                  <c:v>36441742.008875743</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>33600000</c:v>
+                  <c:v>36441742.008875743</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>33600000</c:v>
+                  <c:v>36441742.008875743</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>33600000</c:v>
+                  <c:v>36441742.008875743</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>33600000</c:v>
+                  <c:v>36441742.008875743</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>33600000</c:v>
+                  <c:v>36441742.008875743</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>33600000</c:v>
+                  <c:v>36441742.008875743</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>33600000</c:v>
+                  <c:v>36441742.008875743</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>33600000</c:v>
+                  <c:v>36441742.008875743</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>33600000</c:v>
+                  <c:v>36441742.008875743</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>33600000</c:v>
+                  <c:v>36441742.008875743</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>33600000</c:v>
+                  <c:v>36441742.008875743</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -754,64 +828,64 @@
                 <c:formatCode>"$"#,##0_);[Red]\("$"#,##0\)</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>-324741087</c:v>
+                  <c:v>-281994387</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-291141087</c:v>
+                  <c:v>-245552644.99112427</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-257541087</c:v>
+                  <c:v>-209110902.98224854</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-223941087</c:v>
+                  <c:v>-172669160.97337282</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-190341087</c:v>
+                  <c:v>-136227418.96449709</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-156741087</c:v>
+                  <c:v>-99785676.955621347</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-123141087</c:v>
+                  <c:v>-63343934.946745604</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-89541087</c:v>
+                  <c:v>-26902192.937869862</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-55941087</c:v>
+                  <c:v>9539549.0710058808</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-22341087</c:v>
+                  <c:v>45981291.079881623</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>11258913</c:v>
+                  <c:v>82423033.088757366</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>44858913</c:v>
+                  <c:v>118864775.09763311</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>78458913</c:v>
+                  <c:v>155306517.10650885</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>112058913</c:v>
+                  <c:v>191748259.11538458</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>145658913</c:v>
+                  <c:v>228190001.12426031</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>179258913</c:v>
+                  <c:v>264631743.13313603</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>212858913</c:v>
+                  <c:v>301073485.14201176</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>246458913</c:v>
+                  <c:v>337515227.15088749</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>280058913</c:v>
+                  <c:v>373956969.15976322</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>313658913</c:v>
+                  <c:v>410398711.16863894</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -936,7 +1010,7 @@
                         <c:v>19</c:v>
                       </c:pt>
                       <c:pt idx="19">
-                        <c:v>19</c:v>
+                        <c:v>20</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -2051,14 +2125,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <f>188299170+50000000</f>
-        <v>238299170</v>
-      </c>
-      <c r="C2" s="19">
+        <f>188299170+5000000</f>
+        <v>193299170</v>
+      </c>
+      <c r="C2" s="18">
         <f t="shared" ref="C2" si="0">B2*1.1</f>
-        <v>262129087.00000003</v>
-      </c>
-      <c r="D2" s="3" t="s">
+        <v>212629087.00000003</v>
+      </c>
+      <c r="D2" s="21" t="s">
         <v>0</v>
       </c>
     </row>
@@ -2072,13 +2146,16 @@
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{9A50C6FB-7EC3-47F5-8CDA-3371F386B738}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55B1E273-002F-44CB-B87B-B9FBB131734B}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" style="4" customWidth="1"/>
@@ -2088,23 +2165,23 @@
     <col min="5" max="5" width="14.85546875" style="4" customWidth="1"/>
     <col min="6" max="6" width="11.42578125" style="4"/>
     <col min="7" max="7" width="45.140625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="15" style="4" customWidth="1"/>
+    <col min="8" max="8" width="24.140625" style="4" customWidth="1"/>
     <col min="9" max="16384" width="11.42578125" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="D1" s="20" t="s">
+      <c r="B1" s="26"/>
+      <c r="D1" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="20"/>
-      <c r="G1" s="20" t="s">
+      <c r="E1" s="26"/>
+      <c r="G1" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="20"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2136,7 +2213,7 @@
       <c r="B3" s="5">
         <v>5000000</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="19" t="s">
         <v>35</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -2144,16 +2221,16 @@
       </c>
       <c r="E3" s="4">
         <f>Adquisiciones!C2</f>
-        <v>262129087.00000003</v>
+        <v>212629087.00000003</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="H3" s="4">
-        <f>3000000*12*2</f>
-        <v>72000000</v>
-      </c>
-      <c r="I3" s="23" t="s">
+        <f>1265988*12*4</f>
+        <v>60767424</v>
+      </c>
+      <c r="I3" s="19" t="s">
         <v>37</v>
       </c>
       <c r="J3" s="4" t="s">
@@ -2165,8 +2242,11 @@
         <v>9</v>
       </c>
       <c r="B4" s="5">
-        <f>(9)*16*750*300</f>
-        <v>32400000</v>
+        <f>(9)*14.8333*750*300</f>
+        <v>30037432.5</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>0</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>16</v>
@@ -2175,15 +2255,15 @@
         <f>(2236+3904+2236+2236)*1000</f>
         <v>10612000</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="19" t="s">
         <v>36</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H4" s="4">
-        <f>5000000</f>
-        <v>5000000</v>
+        <f>1000*3*300</f>
+        <v>900000</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>33</v>
@@ -2194,8 +2274,11 @@
         <v>6</v>
       </c>
       <c r="B5" s="5">
-        <f>2500*4000</f>
-        <v>10000000</v>
+        <f>2652*4328</f>
+        <v>11477856</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>40</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>17</v>
@@ -2204,14 +2287,15 @@
         <f>(10000)*4000</f>
         <v>40000000</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="19" t="s">
         <v>35</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>13</v>
       </c>
       <c r="H5" s="4">
-        <v>5000000</v>
+        <f>1000*1*300</f>
+        <v>300000</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>33</v>
@@ -2229,47 +2313,240 @@
         <v>34</v>
       </c>
       <c r="E6" s="4">
-        <f>6*2000000</f>
-        <v>12000000</v>
+        <f>E21*6</f>
+        <v>18753300</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>47</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H6" s="4">
-        <v>5000000</v>
+        <f>H16</f>
+        <v>4608000</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="B7" s="5">
-        <f>SUM(B3:B6)</f>
-        <v>53400000</v>
+        <f>7200*3500</f>
+        <v>25200000</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="E7" s="4">
-        <f>SUM(E3:E6)</f>
-        <v>324741087</v>
+        <v>500000</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="H7" s="4">
-        <f xml:space="preserve"> SUM(H3:H6)</f>
-        <v>87000000</v>
+        <f>20000*14.8333*1500*300*(153/9126)*1%</f>
+        <v>22381606.508875739</v>
+      </c>
+      <c r="I7" s="19" t="s">
+        <v>55</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>33</v>
       </c>
     </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J8" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J9" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J10" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="5">
+        <f>SUM(B3:B6)</f>
+        <v>52515288.5</v>
+      </c>
+      <c r="E11" s="4">
+        <f>SUM(E3:E6)</f>
+        <v>281994387</v>
+      </c>
+      <c r="H11" s="4">
+        <f xml:space="preserve"> SUM(H3:H10)</f>
+        <v>88957030.508875743</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J12" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D13" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="28"/>
+      <c r="G13" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="28"/>
+      <c r="J13" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D14" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D15" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="23">
+        <v>2500000</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H15" s="4">
+        <f>1500*384</f>
+        <v>576000</v>
+      </c>
+      <c r="I15" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D16" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="23">
+        <f>E15*0.522%</f>
+        <v>13050</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16" s="4">
+        <f>H15*(8)</f>
+        <v>4608000</v>
+      </c>
+      <c r="I16" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D17" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="23">
+        <f>E15*12%</f>
+        <v>300000</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D18" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="23">
+        <f>E15*8.5%</f>
+        <v>212500.00000000003</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D19" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="5">
+        <f>E15*4%</f>
+        <v>100000</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="E20" s="5"/>
+      <c r="J20" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="E21" s="5">
+        <f>SUM(E15:E19)</f>
+        <v>3125550</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="J22" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="G13:H13"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F5" r:id="rId1" xr:uid="{ADF784E2-68FC-4B2E-BCC1-790BF86EB68D}"/>
     <hyperlink ref="F4" r:id="rId2" xr:uid="{56839E54-40A4-4628-8AAC-3904428C1DDE}"/>
-    <hyperlink ref="I3" r:id="rId3" xr:uid="{B11B17C2-FF5D-44CB-B7DB-FF30F443A4AC}"/>
+    <hyperlink ref="I3" r:id="rId3" display="https://www.paxiom.com/blogs/robotic-palletizing/" xr:uid="{B11B17C2-FF5D-44CB-B7DB-FF30F443A4AC}"/>
     <hyperlink ref="C3" r:id="rId4" xr:uid="{EAE665CA-5E6D-4F56-A17C-97822EF828F6}"/>
+    <hyperlink ref="C4" r:id="rId5" xr:uid="{AE4BA1C4-2BD4-4E3A-98D1-F571448FB367}"/>
+    <hyperlink ref="C5" r:id="rId6" xr:uid="{DAC22628-7587-405A-821C-8FD093999B7B}"/>
+    <hyperlink ref="C7" r:id="rId7" xr:uid="{D0AD06A3-27EC-4EF4-8201-4A922DF1BF7F}"/>
+    <hyperlink ref="F6" r:id="rId8" xr:uid="{77411267-9DF1-4BF9-8CB5-16F9F931E1E3}"/>
+    <hyperlink ref="I15" r:id="rId9" xr:uid="{3F698569-B7A3-4FE9-A295-16D1DD181AB5}"/>
+    <hyperlink ref="I16" r:id="rId10" xr:uid="{A8CC7652-D463-4B39-85DA-F88E61FBB6D7}"/>
+    <hyperlink ref="I7" r:id="rId11" xr:uid="{C3F8E9A8-E9E9-4A4B-B96B-77303F74F2DD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2310,19 +2587,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="7">
-        <f>'EX+B'!E7*-1</f>
-        <v>-324741087</v>
+        <f>'EX+B'!E11*-1</f>
+        <v>-281994387</v>
       </c>
       <c r="C2" s="15">
         <v>0</v>
       </c>
       <c r="D2" s="15">
         <f t="shared" ref="D2:D21" si="0">SUM(B2:C2)</f>
-        <v>-324741087</v>
+        <v>-281994387</v>
       </c>
       <c r="E2" s="15">
         <f>D2</f>
-        <v>-324741087</v>
+        <v>-281994387</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2330,20 +2607,20 @@
         <v>2</v>
       </c>
       <c r="B3" s="7">
-        <f>'EX+B'!B7*-1</f>
-        <v>-53400000</v>
+        <f>'EX+B'!B11*-1</f>
+        <v>-52515288.5</v>
       </c>
       <c r="C3" s="15">
-        <f>'EX+B'!H7</f>
-        <v>87000000</v>
+        <f>'EX+B'!H11</f>
+        <v>88957030.508875743</v>
       </c>
       <c r="D3" s="15">
-        <f t="shared" si="0"/>
-        <v>33600000</v>
+        <f>SUM(B3:C3)</f>
+        <v>36441742.008875743</v>
       </c>
       <c r="E3" s="15">
         <f>E2+D3</f>
-        <v>-291141087</v>
+        <v>-245552644.99112427</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2352,19 +2629,19 @@
       </c>
       <c r="B4" s="7">
         <f>B3</f>
-        <v>-53400000</v>
+        <v>-52515288.5</v>
       </c>
       <c r="C4" s="15">
         <f>C3</f>
-        <v>87000000</v>
+        <v>88957030.508875743</v>
       </c>
       <c r="D4" s="15">
         <f t="shared" si="0"/>
-        <v>33600000</v>
+        <v>36441742.008875743</v>
       </c>
       <c r="E4" s="15">
         <f t="shared" ref="E4:E21" si="1">E3+D4</f>
-        <v>-257541087</v>
+        <v>-209110902.98224854</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2373,19 +2650,19 @@
       </c>
       <c r="B5" s="7">
         <f t="shared" ref="B5:B19" si="2">B4</f>
-        <v>-53400000</v>
+        <v>-52515288.5</v>
       </c>
       <c r="C5" s="15">
         <f t="shared" ref="C5:C21" si="3">C4</f>
-        <v>87000000</v>
+        <v>88957030.508875743</v>
       </c>
       <c r="D5" s="15">
         <f t="shared" si="0"/>
-        <v>33600000</v>
+        <v>36441742.008875743</v>
       </c>
       <c r="E5" s="15">
         <f t="shared" si="1"/>
-        <v>-223941087</v>
+        <v>-172669160.97337282</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -2394,19 +2671,19 @@
       </c>
       <c r="B6" s="7">
         <f t="shared" si="2"/>
-        <v>-53400000</v>
+        <v>-52515288.5</v>
       </c>
       <c r="C6" s="15">
         <f t="shared" si="3"/>
-        <v>87000000</v>
+        <v>88957030.508875743</v>
       </c>
       <c r="D6" s="15">
         <f t="shared" si="0"/>
-        <v>33600000</v>
+        <v>36441742.008875743</v>
       </c>
       <c r="E6" s="15">
         <f t="shared" si="1"/>
-        <v>-190341087</v>
+        <v>-136227418.96449709</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2415,19 +2692,19 @@
       </c>
       <c r="B7" s="7">
         <f t="shared" si="2"/>
-        <v>-53400000</v>
+        <v>-52515288.5</v>
       </c>
       <c r="C7" s="15">
         <f t="shared" si="3"/>
-        <v>87000000</v>
+        <v>88957030.508875743</v>
       </c>
       <c r="D7" s="15">
         <f t="shared" si="0"/>
-        <v>33600000</v>
+        <v>36441742.008875743</v>
       </c>
       <c r="E7" s="15">
         <f t="shared" si="1"/>
-        <v>-156741087</v>
+        <v>-99785676.955621347</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2436,19 +2713,19 @@
       </c>
       <c r="B8" s="7">
         <f t="shared" si="2"/>
-        <v>-53400000</v>
+        <v>-52515288.5</v>
       </c>
       <c r="C8" s="15">
         <f t="shared" si="3"/>
-        <v>87000000</v>
+        <v>88957030.508875743</v>
       </c>
       <c r="D8" s="15">
         <f t="shared" si="0"/>
-        <v>33600000</v>
+        <v>36441742.008875743</v>
       </c>
       <c r="E8" s="15">
         <f t="shared" si="1"/>
-        <v>-123141087</v>
+        <v>-63343934.946745604</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2457,19 +2734,19 @@
       </c>
       <c r="B9" s="7">
         <f t="shared" si="2"/>
-        <v>-53400000</v>
+        <v>-52515288.5</v>
       </c>
       <c r="C9" s="15">
         <f t="shared" si="3"/>
-        <v>87000000</v>
+        <v>88957030.508875743</v>
       </c>
       <c r="D9" s="15">
         <f t="shared" si="0"/>
-        <v>33600000</v>
+        <v>36441742.008875743</v>
       </c>
       <c r="E9" s="15">
         <f t="shared" si="1"/>
-        <v>-89541087</v>
+        <v>-26902192.937869862</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2478,19 +2755,19 @@
       </c>
       <c r="B10" s="7">
         <f t="shared" si="2"/>
-        <v>-53400000</v>
+        <v>-52515288.5</v>
       </c>
       <c r="C10" s="15">
         <f t="shared" si="3"/>
-        <v>87000000</v>
+        <v>88957030.508875743</v>
       </c>
       <c r="D10" s="15">
         <f t="shared" si="0"/>
-        <v>33600000</v>
+        <v>36441742.008875743</v>
       </c>
       <c r="E10" s="15">
         <f t="shared" si="1"/>
-        <v>-55941087</v>
+        <v>9539549.0710058808</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2499,19 +2776,19 @@
       </c>
       <c r="B11" s="7">
         <f t="shared" si="2"/>
-        <v>-53400000</v>
+        <v>-52515288.5</v>
       </c>
       <c r="C11" s="15">
         <f t="shared" si="3"/>
-        <v>87000000</v>
+        <v>88957030.508875743</v>
       </c>
       <c r="D11" s="15">
         <f t="shared" si="0"/>
-        <v>33600000</v>
+        <v>36441742.008875743</v>
       </c>
       <c r="E11" s="15">
         <f t="shared" si="1"/>
-        <v>-22341087</v>
+        <v>45981291.079881623</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2520,19 +2797,19 @@
       </c>
       <c r="B12" s="7">
         <f t="shared" si="2"/>
-        <v>-53400000</v>
+        <v>-52515288.5</v>
       </c>
       <c r="C12" s="15">
         <f t="shared" si="3"/>
-        <v>87000000</v>
+        <v>88957030.508875743</v>
       </c>
       <c r="D12" s="15">
         <f t="shared" si="0"/>
-        <v>33600000</v>
+        <v>36441742.008875743</v>
       </c>
       <c r="E12" s="15">
         <f t="shared" si="1"/>
-        <v>11258913</v>
+        <v>82423033.088757366</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2541,19 +2818,19 @@
       </c>
       <c r="B13" s="7">
         <f t="shared" si="2"/>
-        <v>-53400000</v>
+        <v>-52515288.5</v>
       </c>
       <c r="C13" s="15">
         <f t="shared" si="3"/>
-        <v>87000000</v>
+        <v>88957030.508875743</v>
       </c>
       <c r="D13" s="15">
         <f t="shared" si="0"/>
-        <v>33600000</v>
+        <v>36441742.008875743</v>
       </c>
       <c r="E13" s="15">
         <f t="shared" si="1"/>
-        <v>44858913</v>
+        <v>118864775.09763311</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2562,19 +2839,19 @@
       </c>
       <c r="B14" s="7">
         <f t="shared" si="2"/>
-        <v>-53400000</v>
+        <v>-52515288.5</v>
       </c>
       <c r="C14" s="15">
         <f t="shared" si="3"/>
-        <v>87000000</v>
+        <v>88957030.508875743</v>
       </c>
       <c r="D14" s="15">
         <f t="shared" si="0"/>
-        <v>33600000</v>
+        <v>36441742.008875743</v>
       </c>
       <c r="E14" s="15">
         <f t="shared" si="1"/>
-        <v>78458913</v>
+        <v>155306517.10650885</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2583,19 +2860,19 @@
       </c>
       <c r="B15" s="7">
         <f t="shared" si="2"/>
-        <v>-53400000</v>
+        <v>-52515288.5</v>
       </c>
       <c r="C15" s="15">
         <f t="shared" si="3"/>
-        <v>87000000</v>
+        <v>88957030.508875743</v>
       </c>
       <c r="D15" s="15">
         <f t="shared" si="0"/>
-        <v>33600000</v>
+        <v>36441742.008875743</v>
       </c>
       <c r="E15" s="15">
         <f t="shared" si="1"/>
-        <v>112058913</v>
+        <v>191748259.11538458</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2604,19 +2881,19 @@
       </c>
       <c r="B16" s="7">
         <f t="shared" si="2"/>
-        <v>-53400000</v>
+        <v>-52515288.5</v>
       </c>
       <c r="C16" s="15">
         <f t="shared" si="3"/>
-        <v>87000000</v>
+        <v>88957030.508875743</v>
       </c>
       <c r="D16" s="15">
         <f t="shared" si="0"/>
-        <v>33600000</v>
+        <v>36441742.008875743</v>
       </c>
       <c r="E16" s="15">
         <f t="shared" si="1"/>
-        <v>145658913</v>
+        <v>228190001.12426031</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -2625,19 +2902,19 @@
       </c>
       <c r="B17" s="7">
         <f t="shared" si="2"/>
-        <v>-53400000</v>
+        <v>-52515288.5</v>
       </c>
       <c r="C17" s="15">
         <f t="shared" si="3"/>
-        <v>87000000</v>
+        <v>88957030.508875743</v>
       </c>
       <c r="D17" s="15">
         <f t="shared" si="0"/>
-        <v>33600000</v>
+        <v>36441742.008875743</v>
       </c>
       <c r="E17" s="15">
         <f t="shared" si="1"/>
-        <v>179258913</v>
+        <v>264631743.13313603</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -2646,19 +2923,19 @@
       </c>
       <c r="B18" s="7">
         <f t="shared" si="2"/>
-        <v>-53400000</v>
+        <v>-52515288.5</v>
       </c>
       <c r="C18" s="15">
         <f t="shared" si="3"/>
-        <v>87000000</v>
+        <v>88957030.508875743</v>
       </c>
       <c r="D18" s="15">
         <f t="shared" si="0"/>
-        <v>33600000</v>
+        <v>36441742.008875743</v>
       </c>
       <c r="E18" s="15">
         <f t="shared" si="1"/>
-        <v>212858913</v>
+        <v>301073485.14201176</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -2667,19 +2944,19 @@
       </c>
       <c r="B19" s="7">
         <f t="shared" si="2"/>
-        <v>-53400000</v>
+        <v>-52515288.5</v>
       </c>
       <c r="C19" s="15">
         <f t="shared" si="3"/>
-        <v>87000000</v>
+        <v>88957030.508875743</v>
       </c>
       <c r="D19" s="15">
         <f t="shared" si="0"/>
-        <v>33600000</v>
+        <v>36441742.008875743</v>
       </c>
       <c r="E19" s="15">
         <f t="shared" si="1"/>
-        <v>246458913</v>
+        <v>337515227.15088749</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -2688,47 +2965,50 @@
       </c>
       <c r="B20" s="7">
         <f>B19</f>
-        <v>-53400000</v>
+        <v>-52515288.5</v>
       </c>
       <c r="C20" s="15">
         <f t="shared" si="3"/>
-        <v>87000000</v>
+        <v>88957030.508875743</v>
       </c>
       <c r="D20" s="15">
         <f t="shared" si="0"/>
-        <v>33600000</v>
+        <v>36441742.008875743</v>
       </c>
       <c r="E20" s="15">
         <f t="shared" si="1"/>
-        <v>280058913</v>
+        <v>373956969.15976322</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="13">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="7">
         <f>B20</f>
-        <v>-53400000</v>
+        <v>-52515288.5</v>
       </c>
       <c r="C21" s="15">
         <f t="shared" si="3"/>
-        <v>87000000</v>
+        <v>88957030.508875743</v>
       </c>
       <c r="D21" s="15">
         <f t="shared" si="0"/>
-        <v>33600000</v>
+        <v>36441742.008875743</v>
       </c>
       <c r="E21" s="15">
         <f t="shared" si="1"/>
-        <v>313658913</v>
-      </c>
+        <v>410398711.16863894</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="13"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="22"/>
+      <c r="B24" s="25"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
@@ -2743,8 +3023,8 @@
         <v>28</v>
       </c>
       <c r="B26" s="16">
-        <f>-E17/D2</f>
-        <v>0.55200564442281363</v>
+        <f>-B29/D2</f>
+        <v>5.7436774070306618E-2</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -2753,7 +3033,7 @@
       </c>
       <c r="B27" s="16">
         <f>IRR(D2:D17)</f>
-        <v>6.074869593392096E-2</v>
+        <v>9.6997650423591875E-2</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -2761,17 +3041,17 @@
         <v>30</v>
       </c>
       <c r="B28" s="17">
-        <f>A12+(-E12/D12)</f>
-        <v>10.664913303571428</v>
+        <f>A10+(-E10/D10)</f>
+        <v>8.7382246691532348</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="18">
-        <f>NPV(B25,D3:D21)+D2</f>
-        <v>-48272211.440307319</v>
+      <c r="B29" s="20">
+        <f>NPV(B25,D2:D21)</f>
+        <v>16196847.89521361</v>
       </c>
     </row>
   </sheetData>
